--- a/artfynd/A 61561-2021 artfynd.xlsx
+++ b/artfynd/A 61561-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117826801</v>
+        <v>117826698</v>
       </c>
       <c r="B2" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hälltjärnen Östra, Hjd</t>
+          <t>Hälltjärnen östra , Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474833</v>
+        <v>474851</v>
       </c>
       <c r="R2" t="n">
-        <v>6852415</v>
+        <v>6852331</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,11 +756,6 @@
           <t>2024-06-16</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>6 ex</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,22 +769,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut</t>
+          <t>Linda Spjut, Amanda Tas</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117826795</v>
+        <v>117826796</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
+        <v>96791</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hälltjärnen Östra, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474877</v>
+        <v>474842</v>
       </c>
       <c r="R3" t="n">
-        <v>6852351</v>
+        <v>6852341</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +865,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,17 +876,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117826945</v>
+        <v>117826798</v>
       </c>
       <c r="B4" t="n">
-        <v>79596</v>
+        <v>97836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,41 +895,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hälltjärnen östra , Hjd</t>
+          <t>Hälltjärnen Östra, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474802</v>
+        <v>474798</v>
       </c>
       <c r="R4" t="n">
-        <v>6852386</v>
+        <v>6852381</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,35 +961,39 @@
           <t>2024-06-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca 90 ex</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda Spjut, Amanda Tas</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117826698</v>
+        <v>117826945</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>79596</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,20 +1002,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1042,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474851</v>
+        <v>474802</v>
       </c>
       <c r="R5" t="n">
-        <v>6852331</v>
+        <v>6852386</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117826893</v>
+        <v>117826801</v>
       </c>
       <c r="B6" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,41 +1108,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hälltjärnen östra , Hjd</t>
+          <t>Hälltjärnen Östra, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474803</v>
+        <v>474833</v>
       </c>
       <c r="R6" t="n">
-        <v>6852388</v>
+        <v>6852415</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,6 +1178,11 @@
           <t>2024-06-16</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>6 ex</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1199,22 +1196,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linda Spjut, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117826798</v>
+        <v>117826795</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
+        <v>78569</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,38 +1220,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hälltjärnen Östra, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474798</v>
+        <v>474877</v>
       </c>
       <c r="R7" t="n">
-        <v>6852381</v>
+        <v>6852351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,17 +1289,13 @@
           <t>2024-06-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ca 90 ex</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1311,17 +1307,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117826802</v>
+        <v>117826893</v>
       </c>
       <c r="B8" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,21 +1330,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,14 +1353,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hälltjärnen Östra, Hjd</t>
+          <t>Hälltjärnen östra , Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474813</v>
+        <v>474803</v>
       </c>
       <c r="R8" t="n">
-        <v>6852427</v>
+        <v>6852388</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,22 +1408,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut</t>
+          <t>Linda Spjut, Amanda Tas</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117826796</v>
+        <v>117826636</v>
       </c>
       <c r="B9" t="n">
-        <v>96791</v>
+        <v>97836</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,38 +1432,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hälltjärnen Östra, Hjd</t>
+          <t>Hälltjärnen östra, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474842</v>
+        <v>474821</v>
       </c>
       <c r="R9" t="n">
-        <v>6852341</v>
+        <v>6852395</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,25 +1516,26 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut, Amanda Tas</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117826799</v>
+        <v>117826610</v>
       </c>
       <c r="B10" t="n">
         <v>97836</v>
@@ -1559,21 +1568,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hälltjärnen Östra, Hjd</t>
+          <t>Hälltjärnen östra, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474839</v>
+        <v>474812</v>
       </c>
       <c r="R10" t="n">
-        <v>6852406</v>
+        <v>6852391</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,11 +1625,6 @@
           <t>2024-06-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ca 40 ex</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1626,19 +1638,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut</t>
+          <t>Linda Spjut, Amanda Tas</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117826800</v>
+        <v>117826799</v>
       </c>
       <c r="B11" t="n">
         <v>97836</v>
@@ -1682,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474828</v>
+        <v>474839</v>
       </c>
       <c r="R11" t="n">
-        <v>6852420</v>
+        <v>6852406</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,7 +1734,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ca 20 ex</t>
+          <t>Ca 40 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,7 +1762,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117826610</v>
+        <v>117826800</v>
       </c>
       <c r="B12" t="n">
         <v>97836</v>
@@ -1783,29 +1795,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hälltjärnen östra, Hjd</t>
+          <t>Hälltjärnen Östra, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474812</v>
+        <v>474828</v>
       </c>
       <c r="R12" t="n">
-        <v>6852391</v>
+        <v>6852420</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,6 +1844,11 @@
           <t>2024-06-16</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 20 ex</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1853,22 +1862,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda Spjut, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117826636</v>
+        <v>117826802</v>
       </c>
       <c r="B13" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,50 +1886,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hälltjärnen östra, Hjd</t>
+          <t>Hälltjärnen Östra, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474821</v>
+        <v>474813</v>
       </c>
       <c r="R13" t="n">
-        <v>6852395</v>
+        <v>6852427</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1968,12 +1968,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda Spjut, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 61561-2021 artfynd.xlsx
+++ b/artfynd/A 61561-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117826698</v>
+        <v>117826800</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hälltjärnen östra , Hjd</t>
+          <t>Hälltjärnen Östra, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474851</v>
+        <v>474828</v>
       </c>
       <c r="R2" t="n">
-        <v>6852331</v>
+        <v>6852420</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +757,11 @@
           <t>2024-06-16</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca 20 ex</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -769,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linda Spjut, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117826796</v>
+        <v>117826636</v>
       </c>
       <c r="B3" t="n">
-        <v>96791</v>
+        <v>97838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +799,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hälltjärnen Östra, Hjd</t>
+          <t>Hälltjärnen östra, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474842</v>
+        <v>474821</v>
       </c>
       <c r="R3" t="n">
-        <v>6852341</v>
+        <v>6852395</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,28 +883,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut, Amanda Tas</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117826798</v>
+        <v>117826945</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>79598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,38 +914,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hälltjärnen Östra, Hjd</t>
+          <t>Hälltjärnen östra , Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474798</v>
+        <v>474802</v>
       </c>
       <c r="R4" t="n">
-        <v>6852381</v>
+        <v>6852386</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,39 +983,35 @@
           <t>2024-06-16</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca 90 ex</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut, Amanda Tas</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117826945</v>
+        <v>117826796</v>
       </c>
       <c r="B5" t="n">
-        <v>79596</v>
+        <v>96793</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,37 +1024,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hälltjärnen östra , Hjd</t>
+          <t>Hälltjärnen Östra, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474802</v>
+        <v>474842</v>
       </c>
       <c r="R5" t="n">
-        <v>6852386</v>
+        <v>6852341</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,29 +1092,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Spjut, Amanda Tas</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117826801</v>
+        <v>117826798</v>
       </c>
       <c r="B6" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,20 +1144,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hälltjärnen Östra, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474833</v>
+        <v>474798</v>
       </c>
       <c r="R6" t="n">
-        <v>6852415</v>
+        <v>6852381</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,7 +1190,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>6 ex</t>
+          <t>Ca 90 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,7 +1199,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1201,17 +1210,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117826795</v>
+        <v>117826802</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
+        <v>78482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,25 +1229,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474877</v>
+        <v>474813</v>
       </c>
       <c r="R7" t="n">
-        <v>6852351</v>
+        <v>6852427</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117826893</v>
+        <v>117826795</v>
       </c>
       <c r="B8" t="n">
-        <v>79561</v>
+        <v>78571</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,25 +1335,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1353,14 +1362,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hälltjärnen östra , Hjd</t>
+          <t>Hälltjärnen Östra, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474803</v>
+        <v>474877</v>
       </c>
       <c r="R8" t="n">
-        <v>6852388</v>
+        <v>6852351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,22 +1417,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda Spjut, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117826636</v>
+        <v>117826698</v>
       </c>
       <c r="B9" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,50 +1441,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hälltjärnen östra, Hjd</t>
+          <t>Hälltjärnen östra , Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474821</v>
+        <v>474851</v>
       </c>
       <c r="R9" t="n">
-        <v>6852395</v>
+        <v>6852331</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1538,7 @@
         <v>117826610</v>
       </c>
       <c r="B10" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117826799</v>
+        <v>117826893</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,42 +1662,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hälltjärnen Östra, Hjd</t>
+          <t>Hälltjärnen östra , Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474839</v>
+        <v>474803</v>
       </c>
       <c r="R11" t="n">
-        <v>6852406</v>
+        <v>6852388</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,11 +1731,6 @@
           <t>2024-06-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 40 ex</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1750,22 +1744,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut</t>
+          <t>Linda Spjut, Amanda Tas</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117826800</v>
+        <v>117826801</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474828</v>
+        <v>474833</v>
       </c>
       <c r="R12" t="n">
-        <v>6852420</v>
+        <v>6852415</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,7 +1840,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ca 20 ex</t>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117826802</v>
+        <v>117826799</v>
       </c>
       <c r="B13" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1886,30 +1880,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1917,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474813</v>
+        <v>474839</v>
       </c>
       <c r="R13" t="n">
-        <v>6852427</v>
+        <v>6852406</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,6 +1948,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ca 40 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 61561-2021 artfynd.xlsx
+++ b/artfynd/A 61561-2021 artfynd.xlsx
@@ -2299,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118680319</v>
+        <v>118680288</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>78518</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,42 +2311,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474434</v>
+        <v>474435</v>
       </c>
       <c r="R17" t="n">
-        <v>6852667</v>
+        <v>6852671</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,7 +2383,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2410,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118680288</v>
+        <v>118680319</v>
       </c>
       <c r="B18" t="n">
-        <v>78518</v>
+        <v>97846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,38 +2417,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474435</v>
+        <v>474434</v>
       </c>
       <c r="R18" t="n">
-        <v>6852671</v>
+        <v>6852667</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,6 +2493,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118680171</v>
+        <v>118679617</v>
       </c>
       <c r="B39" t="n">
-        <v>97846</v>
+        <v>78518</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4731,50 +4731,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474698</v>
+        <v>474427</v>
       </c>
       <c r="R39" t="n">
-        <v>6852578</v>
+        <v>6852576</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4815,7 +4803,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4827,7 +4814,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4838,10 +4825,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118680127</v>
+        <v>118679700</v>
       </c>
       <c r="B40" t="n">
-        <v>97846</v>
+        <v>79469</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4850,46 +4837,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474730</v>
+        <v>474495</v>
       </c>
       <c r="R40" t="n">
-        <v>6852558</v>
+        <v>6852676</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4924,18 +4903,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4958,10 +4931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118679617</v>
+        <v>118679735</v>
       </c>
       <c r="B41" t="n">
-        <v>78518</v>
+        <v>79565</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4974,21 +4947,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4998,10 +4971,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474427</v>
+        <v>474779</v>
       </c>
       <c r="R41" t="n">
-        <v>6852576</v>
+        <v>6852423</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5053,7 +5026,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5064,10 +5037,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118679700</v>
+        <v>118680171</v>
       </c>
       <c r="B42" t="n">
-        <v>79469</v>
+        <v>97846</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5076,38 +5049,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474495</v>
+        <v>474698</v>
       </c>
       <c r="R42" t="n">
-        <v>6852676</v>
+        <v>6852578</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5148,6 +5133,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5170,10 +5156,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118679735</v>
+        <v>118680127</v>
       </c>
       <c r="B43" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5182,38 +5168,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474779</v>
+        <v>474730</v>
       </c>
       <c r="R43" t="n">
-        <v>6852423</v>
+        <v>6852558</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5248,12 +5242,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61561-2021 artfynd.xlsx
+++ b/artfynd/A 61561-2021 artfynd.xlsx
@@ -2728,7 +2728,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118680183</v>
+        <v>118680130</v>
       </c>
       <c r="B21" t="n">
         <v>97846</v>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474905</v>
+        <v>474469</v>
       </c>
       <c r="R21" t="n">
-        <v>6852317</v>
+        <v>6852587</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2848,7 +2848,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118680130</v>
+        <v>118680183</v>
       </c>
       <c r="B22" t="n">
         <v>97846</v>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474469</v>
+        <v>474905</v>
       </c>
       <c r="R22" t="n">
-        <v>6852587</v>
+        <v>6852317</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3843,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118680129</v>
+        <v>118679940</v>
       </c>
       <c r="B31" t="n">
-        <v>97846</v>
+        <v>78129</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3855,46 +3855,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474707</v>
+        <v>474472</v>
       </c>
       <c r="R31" t="n">
-        <v>6852573</v>
+        <v>6852583</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3929,18 +3921,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3963,10 +3949,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118679940</v>
+        <v>118679621</v>
       </c>
       <c r="B32" t="n">
-        <v>78129</v>
+        <v>78518</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3979,21 +3965,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4003,10 +3989,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474472</v>
+        <v>474466</v>
       </c>
       <c r="R32" t="n">
-        <v>6852583</v>
+        <v>6852701</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4058,7 +4044,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4069,10 +4055,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118679621</v>
+        <v>118680129</v>
       </c>
       <c r="B33" t="n">
-        <v>78518</v>
+        <v>97846</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4081,38 +4067,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474466</v>
+        <v>474707</v>
       </c>
       <c r="R33" t="n">
-        <v>6852701</v>
+        <v>6852573</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4147,12 +4141,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -5594,10 +5594,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118679619</v>
+        <v>118680137</v>
       </c>
       <c r="B47" t="n">
-        <v>78518</v>
+        <v>97846</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5606,38 +5606,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474495</v>
+        <v>474644</v>
       </c>
       <c r="R47" t="n">
-        <v>6852672</v>
+        <v>6852619</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5672,12 +5680,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5689,7 +5703,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5700,10 +5714,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118680137</v>
+        <v>118679619</v>
       </c>
       <c r="B48" t="n">
-        <v>97846</v>
+        <v>78518</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5712,46 +5726,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474644</v>
+        <v>474495</v>
       </c>
       <c r="R48" t="n">
-        <v>6852619</v>
+        <v>6852672</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5786,18 +5792,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">

--- a/artfynd/A 61561-2021 artfynd.xlsx
+++ b/artfynd/A 61561-2021 artfynd.xlsx
@@ -2188,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118680321</v>
+        <v>118680319</v>
       </c>
       <c r="B16" t="n">
         <v>97846</v>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2235,7 +2235,7 @@
         <v>474434</v>
       </c>
       <c r="R16" t="n">
-        <v>6852636</v>
+        <v>6852667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118680288</v>
+        <v>118680321</v>
       </c>
       <c r="B17" t="n">
-        <v>78518</v>
+        <v>97846</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,38 +2311,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474435</v>
+        <v>474434</v>
       </c>
       <c r="R17" t="n">
-        <v>6852671</v>
+        <v>6852636</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2383,6 +2387,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2405,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118680319</v>
+        <v>118680288</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>78518</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,42 +2422,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474434</v>
+        <v>474435</v>
       </c>
       <c r="R18" t="n">
-        <v>6852667</v>
+        <v>6852671</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,7 +2494,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118679657</v>
+        <v>118658645</v>
       </c>
       <c r="B19" t="n">
-        <v>79102</v>
+        <v>79565</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2532,37 +2532,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474472</v>
+        <v>474572</v>
       </c>
       <c r="R19" t="n">
-        <v>6852583</v>
+        <v>6852630</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2622,10 +2622,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118658645</v>
+        <v>118680180</v>
       </c>
       <c r="B20" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,41 +2634,53 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474572</v>
+        <v>474813</v>
       </c>
       <c r="R20" t="n">
-        <v>6852630</v>
+        <v>6852408</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2692,12 +2704,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,6 +2718,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2717,7 +2730,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2728,10 +2741,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118680130</v>
+        <v>118679735</v>
       </c>
       <c r="B21" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2740,46 +2753,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474469</v>
+        <v>474779</v>
       </c>
       <c r="R21" t="n">
-        <v>6852587</v>
+        <v>6852423</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,18 +2819,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2848,10 +2847,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118680183</v>
+        <v>118679724</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>78221</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2860,46 +2859,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474905</v>
+        <v>474329</v>
       </c>
       <c r="R22" t="n">
-        <v>6852317</v>
+        <v>6852451</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,18 +2925,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2968,10 +2953,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118679724</v>
+        <v>118679618</v>
       </c>
       <c r="B23" t="n">
-        <v>78221</v>
+        <v>78518</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2984,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3008,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474329</v>
+        <v>474423</v>
       </c>
       <c r="R23" t="n">
-        <v>6852451</v>
+        <v>6852576</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3063,7 +3048,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3074,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118679618</v>
+        <v>118679736</v>
       </c>
       <c r="B24" t="n">
-        <v>78518</v>
+        <v>79565</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3090,21 +3075,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3114,10 +3099,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474423</v>
+        <v>474798</v>
       </c>
       <c r="R24" t="n">
-        <v>6852576</v>
+        <v>6852414</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3169,7 +3154,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3180,10 +3165,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118679941</v>
+        <v>118680128</v>
       </c>
       <c r="B25" t="n">
-        <v>78129</v>
+        <v>97846</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,38 +3177,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474458</v>
+        <v>474753</v>
       </c>
       <c r="R25" t="n">
-        <v>6852586</v>
+        <v>6852510</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3258,12 +3251,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1 blomstjälk, på nyligen upptaget kalhygge, Stora Enso</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3286,10 +3285,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118658643</v>
+        <v>118679619</v>
       </c>
       <c r="B26" t="n">
-        <v>79565</v>
+        <v>78518</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,37 +3301,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474573</v>
+        <v>474495</v>
       </c>
       <c r="R26" t="n">
-        <v>6852666</v>
+        <v>6852672</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3356,12 +3355,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3392,10 +3391,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118680179</v>
+        <v>118658622</v>
       </c>
       <c r="B27" t="n">
-        <v>97846</v>
+        <v>79566</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,53 +3403,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474779</v>
+        <v>474551</v>
       </c>
       <c r="R27" t="n">
-        <v>6852421</v>
+        <v>6852613</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3474,12 +3461,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3488,7 +3475,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3500,7 +3486,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3511,10 +3497,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118679759</v>
+        <v>118679621</v>
       </c>
       <c r="B28" t="n">
-        <v>79565</v>
+        <v>78518</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3527,21 +3513,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3551,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474450</v>
+        <v>474466</v>
       </c>
       <c r="R28" t="n">
-        <v>6852713</v>
+        <v>6852701</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3606,7 +3592,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3617,10 +3603,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118680174</v>
+        <v>118679758</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3629,46 +3615,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474644</v>
+        <v>474422</v>
       </c>
       <c r="R29" t="n">
-        <v>6852601</v>
+        <v>6852578</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3703,18 +3681,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3737,10 +3709,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118679758</v>
+        <v>118680137</v>
       </c>
       <c r="B30" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3749,38 +3721,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474422</v>
+        <v>474644</v>
       </c>
       <c r="R30" t="n">
-        <v>6852578</v>
+        <v>6852619</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3815,12 +3795,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3843,10 +3829,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118679940</v>
+        <v>118679945</v>
       </c>
       <c r="B31" t="n">
-        <v>78129</v>
+        <v>91779</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3855,25 +3841,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3883,10 +3869,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474472</v>
+        <v>474746</v>
       </c>
       <c r="R31" t="n">
-        <v>6852583</v>
+        <v>6852534</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3949,10 +3935,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118679621</v>
+        <v>118680130</v>
       </c>
       <c r="B32" t="n">
-        <v>78518</v>
+        <v>97846</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3961,38 +3947,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474466</v>
+        <v>474469</v>
       </c>
       <c r="R32" t="n">
-        <v>6852701</v>
+        <v>6852587</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4027,12 +4021,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4175,10 +4175,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118679942</v>
+        <v>118679617</v>
       </c>
       <c r="B34" t="n">
-        <v>78129</v>
+        <v>78518</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4191,21 +4191,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474458</v>
+        <v>474427</v>
       </c>
       <c r="R34" t="n">
-        <v>6852705</v>
+        <v>6852576</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4281,10 +4281,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118679694</v>
+        <v>118679960</v>
       </c>
       <c r="B35" t="n">
-        <v>78573</v>
+        <v>91070</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4293,38 +4293,49 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6450</v>
+        <v>760</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474864</v>
+        <v>474694</v>
       </c>
       <c r="R35" t="n">
-        <v>6852352</v>
+        <v>6852440</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4359,12 +4370,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Vid hyggeskant</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4387,10 +4404,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118679642</v>
+        <v>118679947</v>
       </c>
       <c r="B36" t="n">
-        <v>79102</v>
+        <v>91779</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4399,25 +4416,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4427,10 +4444,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474823</v>
+        <v>474722</v>
       </c>
       <c r="R36" t="n">
-        <v>6852408</v>
+        <v>6852456</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4493,10 +4510,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118680138</v>
+        <v>118679941</v>
       </c>
       <c r="B37" t="n">
-        <v>97846</v>
+        <v>78129</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4505,46 +4522,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474928</v>
+        <v>474458</v>
       </c>
       <c r="R37" t="n">
-        <v>6852284</v>
+        <v>6852586</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4579,18 +4588,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4613,10 +4616,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118658677</v>
+        <v>118679700</v>
       </c>
       <c r="B38" t="n">
-        <v>97846</v>
+        <v>79469</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4625,41 +4628,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474572</v>
+        <v>474495</v>
       </c>
       <c r="R38" t="n">
-        <v>6852669</v>
+        <v>6852676</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4683,12 +4686,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4708,7 +4711,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4719,10 +4722,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118679617</v>
+        <v>118679694</v>
       </c>
       <c r="B39" t="n">
-        <v>78518</v>
+        <v>78573</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4731,25 +4734,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6450</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4759,10 +4762,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474427</v>
+        <v>474864</v>
       </c>
       <c r="R39" t="n">
-        <v>6852576</v>
+        <v>6852352</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4814,7 +4817,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4825,10 +4828,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118679700</v>
+        <v>118679734</v>
       </c>
       <c r="B40" t="n">
-        <v>79469</v>
+        <v>79565</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4837,25 +4840,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4865,10 +4868,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474495</v>
+        <v>474576</v>
       </c>
       <c r="R40" t="n">
-        <v>6852676</v>
+        <v>6852662</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4931,7 +4934,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118679735</v>
+        <v>118679759</v>
       </c>
       <c r="B41" t="n">
         <v>79565</v>
@@ -4971,10 +4974,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474779</v>
+        <v>474450</v>
       </c>
       <c r="R41" t="n">
-        <v>6852423</v>
+        <v>6852713</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5037,7 +5040,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118680171</v>
+        <v>118658677</v>
       </c>
       <c r="B42" t="n">
         <v>97846</v>
@@ -5070,32 +5073,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474698</v>
+        <v>474572</v>
       </c>
       <c r="R42" t="n">
-        <v>6852578</v>
+        <v>6852669</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5119,12 +5110,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5133,7 +5124,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5145,7 +5135,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5156,7 +5146,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118680127</v>
+        <v>118680171</v>
       </c>
       <c r="B43" t="n">
         <v>97846</v>
@@ -5189,13 +5179,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5204,10 +5198,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474730</v>
+        <v>474698</v>
       </c>
       <c r="R43" t="n">
-        <v>6852558</v>
+        <v>6852578</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5240,11 +5234,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5276,10 +5265,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118679947</v>
+        <v>118680127</v>
       </c>
       <c r="B44" t="n">
-        <v>91779</v>
+        <v>97846</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5288,38 +5277,46 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474722</v>
+        <v>474730</v>
       </c>
       <c r="R44" t="n">
-        <v>6852456</v>
+        <v>6852558</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5354,12 +5351,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5382,10 +5385,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118679659</v>
+        <v>118679942</v>
       </c>
       <c r="B45" t="n">
-        <v>79102</v>
+        <v>78129</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5398,21 +5401,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5422,7 +5425,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474456</v>
+        <v>474458</v>
       </c>
       <c r="R45" t="n">
         <v>6852705</v>
@@ -5488,10 +5491,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118658617</v>
+        <v>118680179</v>
       </c>
       <c r="B46" t="n">
-        <v>57443</v>
+        <v>97846</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5500,41 +5503,53 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474552</v>
+        <v>474779</v>
       </c>
       <c r="R46" t="n">
-        <v>6852613</v>
+        <v>6852421</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5558,12 +5573,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5572,6 +5587,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5583,7 +5599,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5594,7 +5610,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118680137</v>
+        <v>118680174</v>
       </c>
       <c r="B47" t="n">
         <v>97846</v>
@@ -5645,7 +5661,7 @@
         <v>474644</v>
       </c>
       <c r="R47" t="n">
-        <v>6852619</v>
+        <v>6852601</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5682,7 +5698,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5714,10 +5730,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118679619</v>
+        <v>118679940</v>
       </c>
       <c r="B48" t="n">
-        <v>78518</v>
+        <v>78129</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5730,21 +5746,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5754,10 +5770,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474495</v>
+        <v>474472</v>
       </c>
       <c r="R48" t="n">
-        <v>6852672</v>
+        <v>6852583</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5809,7 +5825,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5820,7 +5836,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118679734</v>
+        <v>118658643</v>
       </c>
       <c r="B49" t="n">
         <v>79565</v>
@@ -5856,17 +5872,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474576</v>
+        <v>474573</v>
       </c>
       <c r="R49" t="n">
-        <v>6852662</v>
+        <v>6852666</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5890,12 +5906,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5915,7 +5931,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5926,10 +5942,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118679945</v>
+        <v>118680199</v>
       </c>
       <c r="B50" t="n">
-        <v>91779</v>
+        <v>97846</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5938,38 +5954,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474746</v>
+        <v>474451</v>
       </c>
       <c r="R50" t="n">
-        <v>6852534</v>
+        <v>6852701</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6004,12 +6028,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6138,10 +6168,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118679736</v>
+        <v>118680169</v>
       </c>
       <c r="B52" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6150,38 +6180,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474798</v>
+        <v>474444</v>
       </c>
       <c r="R52" t="n">
-        <v>6852414</v>
+        <v>6852693</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6216,12 +6254,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6244,7 +6288,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118680128</v>
+        <v>118680138</v>
       </c>
       <c r="B53" t="n">
         <v>97846</v>
@@ -6292,10 +6336,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474753</v>
+        <v>474928</v>
       </c>
       <c r="R53" t="n">
-        <v>6852510</v>
+        <v>6852284</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6332,7 +6376,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>1 blomstjälk, på nyligen upptaget kalhygge, Stora Enso</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6364,7 +6408,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118680180</v>
+        <v>118680183</v>
       </c>
       <c r="B54" t="n">
         <v>97846</v>
@@ -6397,17 +6441,13 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
@@ -6416,10 +6456,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474813</v>
+        <v>474905</v>
       </c>
       <c r="R54" t="n">
-        <v>6852408</v>
+        <v>6852317</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6452,6 +6492,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6483,10 +6528,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118680199</v>
+        <v>118679642</v>
       </c>
       <c r="B55" t="n">
-        <v>97846</v>
+        <v>79102</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6495,46 +6540,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474451</v>
+        <v>474823</v>
       </c>
       <c r="R55" t="n">
-        <v>6852701</v>
+        <v>6852408</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6569,18 +6606,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6603,10 +6634,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118680169</v>
+        <v>118679659</v>
       </c>
       <c r="B56" t="n">
-        <v>97846</v>
+        <v>79102</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6615,46 +6646,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474444</v>
+        <v>474456</v>
       </c>
       <c r="R56" t="n">
-        <v>6852693</v>
+        <v>6852705</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6689,18 +6712,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6723,10 +6740,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118679960</v>
+        <v>118679657</v>
       </c>
       <c r="B57" t="n">
-        <v>91070</v>
+        <v>79102</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6735,49 +6752,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>760</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474694</v>
+        <v>474472</v>
       </c>
       <c r="R57" t="n">
-        <v>6852440</v>
+        <v>6852583</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6812,18 +6818,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Vid hyggeskant</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118658622</v>
+        <v>118658617</v>
       </c>
       <c r="B58" t="n">
-        <v>79566</v>
+        <v>57443</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6862,21 +6862,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474551</v>
+        <v>474552</v>
       </c>
       <c r="R58" t="n">
         <v>6852613</v>

--- a/artfynd/A 61561-2021 artfynd.xlsx
+++ b/artfynd/A 61561-2021 artfynd.xlsx
@@ -4722,10 +4722,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118679694</v>
+        <v>118679734</v>
       </c>
       <c r="B39" t="n">
-        <v>78573</v>
+        <v>79565</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4734,25 +4734,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474864</v>
+        <v>474576</v>
       </c>
       <c r="R39" t="n">
-        <v>6852352</v>
+        <v>6852662</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4828,7 +4828,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118679734</v>
+        <v>118679759</v>
       </c>
       <c r="B40" t="n">
         <v>79565</v>
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474576</v>
+        <v>474450</v>
       </c>
       <c r="R40" t="n">
-        <v>6852662</v>
+        <v>6852713</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4934,10 +4934,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118679759</v>
+        <v>118679694</v>
       </c>
       <c r="B41" t="n">
-        <v>79565</v>
+        <v>78573</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4946,25 +4946,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4974,10 +4974,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474450</v>
+        <v>474864</v>
       </c>
       <c r="R41" t="n">
-        <v>6852713</v>
+        <v>6852352</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5146,10 +5146,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118680171</v>
+        <v>118679942</v>
       </c>
       <c r="B43" t="n">
-        <v>97846</v>
+        <v>78129</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5158,50 +5158,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474698</v>
+        <v>474458</v>
       </c>
       <c r="R43" t="n">
-        <v>6852578</v>
+        <v>6852705</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5242,7 +5230,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5385,10 +5372,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118679942</v>
+        <v>118680171</v>
       </c>
       <c r="B45" t="n">
-        <v>78129</v>
+        <v>97846</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5397,38 +5384,50 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474458</v>
+        <v>474698</v>
       </c>
       <c r="R45" t="n">
-        <v>6852705</v>
+        <v>6852578</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5469,6 +5468,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6288,10 +6288,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118680138</v>
+        <v>118679642</v>
       </c>
       <c r="B53" t="n">
-        <v>97846</v>
+        <v>79102</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6300,46 +6300,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474928</v>
+        <v>474823</v>
       </c>
       <c r="R53" t="n">
-        <v>6852284</v>
+        <v>6852408</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6374,18 +6366,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6408,7 +6394,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118680183</v>
+        <v>118680138</v>
       </c>
       <c r="B54" t="n">
         <v>97846</v>
@@ -6456,10 +6442,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474905</v>
+        <v>474928</v>
       </c>
       <c r="R54" t="n">
-        <v>6852317</v>
+        <v>6852284</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6496,7 +6482,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6528,10 +6514,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118679642</v>
+        <v>118680183</v>
       </c>
       <c r="B55" t="n">
-        <v>79102</v>
+        <v>97846</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6540,38 +6526,46 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474823</v>
+        <v>474905</v>
       </c>
       <c r="R55" t="n">
-        <v>6852408</v>
+        <v>6852317</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6606,12 +6600,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61561-2021 artfynd.xlsx
+++ b/artfynd/A 61561-2021 artfynd.xlsx
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118680304</v>
+        <v>118680288</v>
       </c>
       <c r="B14" t="n">
-        <v>78221</v>
+        <v>78518</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1996,21 +1996,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474415</v>
+        <v>474435</v>
       </c>
       <c r="R14" t="n">
         <v>6852671</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118682042</v>
+        <v>118680304</v>
       </c>
       <c r="B15" t="n">
-        <v>78129</v>
+        <v>78221</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2102,37 +2102,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fågelsjö 7 mellan, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474472</v>
+        <v>474415</v>
       </c>
       <c r="R15" t="n">
-        <v>6852580</v>
+        <v>6852671</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2176,22 +2176,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Klara Li Yngve</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>August Lindberg, Jana Eriksson, Philipp Weiss, Klara Li Yngve</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Klara Li Yngve, Philipp Weiss, Jana Eriksson, August Lindberg, diana spjut, Ann-Charlotte Svensson, Emma Sewell</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118680319</v>
+        <v>118682042</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>78129</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,45 +2204,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Fågelsjö 7 mellan, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474434</v>
+        <v>474472</v>
       </c>
       <c r="R16" t="n">
-        <v>6852667</v>
+        <v>6852580</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2276,26 +2276,21 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Klara Li Yngve</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Klara Li Yngve, Philipp Weiss, Jana Eriksson, August Lindberg, diana spjut, Ann-Charlotte Svensson, Emma Sewell</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>August Lindberg, Jana Eriksson, Philipp Weiss, Klara Li Yngve</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2410,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118680288</v>
+        <v>118680319</v>
       </c>
       <c r="B18" t="n">
-        <v>78518</v>
+        <v>97846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,38 +2417,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474435</v>
+        <v>474434</v>
       </c>
       <c r="R18" t="n">
-        <v>6852671</v>
+        <v>6852667</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,6 +2493,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118658645</v>
+        <v>118680183</v>
       </c>
       <c r="B19" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2528,41 +2528,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474572</v>
+        <v>474905</v>
       </c>
       <c r="R19" t="n">
-        <v>6852630</v>
+        <v>6852317</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2586,12 +2594,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2600,6 +2613,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2611,7 +2625,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2622,10 +2636,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118680180</v>
+        <v>118679734</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,50 +2648,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474813</v>
+        <v>474576</v>
       </c>
       <c r="R20" t="n">
-        <v>6852408</v>
+        <v>6852662</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,7 +2720,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2741,10 +2742,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118679735</v>
+        <v>118679941</v>
       </c>
       <c r="B21" t="n">
-        <v>79565</v>
+        <v>78129</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2757,21 +2758,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2782,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474779</v>
+        <v>474458</v>
       </c>
       <c r="R21" t="n">
-        <v>6852423</v>
+        <v>6852586</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2847,10 +2848,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118679724</v>
+        <v>118679959</v>
       </c>
       <c r="B22" t="n">
-        <v>78221</v>
+        <v>91779</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2859,25 +2860,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2887,10 +2888,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474329</v>
+        <v>474464</v>
       </c>
       <c r="R22" t="n">
-        <v>6852451</v>
+        <v>6852695</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2953,10 +2954,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118679618</v>
+        <v>118658617</v>
       </c>
       <c r="B23" t="n">
-        <v>78518</v>
+        <v>57443</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2969,37 +2970,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474423</v>
+        <v>474552</v>
       </c>
       <c r="R23" t="n">
-        <v>6852576</v>
+        <v>6852613</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3023,12 +3024,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,10 +3060,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118679736</v>
+        <v>118680137</v>
       </c>
       <c r="B24" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3071,38 +3072,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474798</v>
+        <v>474644</v>
       </c>
       <c r="R24" t="n">
-        <v>6852414</v>
+        <v>6852619</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3137,12 +3146,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3165,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118680128</v>
+        <v>118658645</v>
       </c>
       <c r="B25" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3177,49 +3192,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474753</v>
+        <v>474572</v>
       </c>
       <c r="R25" t="n">
-        <v>6852510</v>
+        <v>6852630</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3243,17 +3250,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1 blomstjälk, på nyligen upptaget kalhygge, Stora Enso</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3262,7 +3264,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3274,7 +3275,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3285,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118679619</v>
+        <v>118680169</v>
       </c>
       <c r="B26" t="n">
-        <v>78518</v>
+        <v>97846</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3297,38 +3298,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474495</v>
+        <v>474444</v>
       </c>
       <c r="R26" t="n">
-        <v>6852672</v>
+        <v>6852693</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3363,12 +3372,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3380,7 +3395,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3391,10 +3406,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118658622</v>
+        <v>118680130</v>
       </c>
       <c r="B27" t="n">
-        <v>79566</v>
+        <v>97846</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3403,41 +3418,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474551</v>
+        <v>474469</v>
       </c>
       <c r="R27" t="n">
-        <v>6852613</v>
+        <v>6852587</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3461,12 +3484,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3475,6 +3503,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3486,7 +3515,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3497,10 +3526,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118679621</v>
+        <v>118679759</v>
       </c>
       <c r="B28" t="n">
-        <v>78518</v>
+        <v>79565</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3513,21 +3542,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3537,10 +3566,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474466</v>
+        <v>474450</v>
       </c>
       <c r="R28" t="n">
-        <v>6852701</v>
+        <v>6852713</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3592,7 +3621,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Emma Sewell, Jana Eriksson, Ann-Charlotte Svensson, diana spjut, August Lindberg, Klara Li Yngve</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3603,10 +3632,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118679758</v>
+        <v>118680127</v>
       </c>
       <c r="B29" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3615,38 +3644,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474422</v>
+        <v>474730</v>
       </c>
       <c r="R29" t="n">
-        <v>6852578</v>
+        <v>6852558</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3681,12 +3718,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3709,7 +3752,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118680137</v>
+        <v>118680138</v>
       </c>
       <c r="B30" t="n">
         <v>97846</v>
@@ -3757,10 +3800,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474644</v>
+        <v>474928</v>
       </c>
       <c r="R30" t="n">
-        <v>6852619</v>
+        <v>6852284</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3829,10 +3872,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118679945</v>
+        <v>118679942</v>
       </c>
       <c r="B31" t="n">
-        <v>91779</v>
+        <v>78129</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3841,25 +3884,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3869,10 +3912,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474746</v>
+        <v>474458</v>
       </c>
       <c r="R31" t="n">
-        <v>6852534</v>
+        <v>6852705</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,7 +3978,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118680130</v>
+        <v>118658677</v>
       </c>
       <c r="B32" t="n">
         <v>97846</v>
@@ -3969,27 +4012,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474469</v>
+        <v>474572</v>
       </c>
       <c r="R32" t="n">
-        <v>6852587</v>
+        <v>6852669</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4013,17 +4048,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4032,7 +4062,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4044,7 +4073,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4055,7 +4084,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118680129</v>
+        <v>118680199</v>
       </c>
       <c r="B33" t="n">
         <v>97846</v>
@@ -4103,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474707</v>
+        <v>474451</v>
       </c>
       <c r="R33" t="n">
-        <v>6852573</v>
+        <v>6852701</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4175,10 +4204,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118679617</v>
+        <v>118680179</v>
       </c>
       <c r="B34" t="n">
-        <v>78518</v>
+        <v>97846</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4187,38 +4216,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474427</v>
+        <v>474779</v>
       </c>
       <c r="R34" t="n">
-        <v>6852576</v>
+        <v>6852421</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4259,6 +4300,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4270,7 +4312,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4281,10 +4323,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118679960</v>
+        <v>118680129</v>
       </c>
       <c r="B35" t="n">
-        <v>91070</v>
+        <v>97846</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4297,34 +4339,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4332,10 +4371,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474694</v>
+        <v>474707</v>
       </c>
       <c r="R35" t="n">
-        <v>6852440</v>
+        <v>6852573</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4372,7 +4411,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Vid hyggeskant</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4404,10 +4443,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118679947</v>
+        <v>118679700</v>
       </c>
       <c r="B36" t="n">
-        <v>91779</v>
+        <v>79469</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4420,21 +4459,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4444,10 +4483,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474722</v>
+        <v>474495</v>
       </c>
       <c r="R36" t="n">
-        <v>6852456</v>
+        <v>6852676</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4510,10 +4549,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118679941</v>
+        <v>118679945</v>
       </c>
       <c r="B37" t="n">
-        <v>78129</v>
+        <v>91779</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4522,25 +4561,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4550,10 +4589,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474458</v>
+        <v>474746</v>
       </c>
       <c r="R37" t="n">
-        <v>6852586</v>
+        <v>6852534</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4616,10 +4655,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118679700</v>
+        <v>118679659</v>
       </c>
       <c r="B38" t="n">
-        <v>79469</v>
+        <v>79102</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4628,25 +4667,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4656,10 +4695,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474495</v>
+        <v>474456</v>
       </c>
       <c r="R38" t="n">
-        <v>6852676</v>
+        <v>6852705</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4722,7 +4761,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118679734</v>
+        <v>118658643</v>
       </c>
       <c r="B39" t="n">
         <v>79565</v>
@@ -4758,17 +4797,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474576</v>
+        <v>474573</v>
       </c>
       <c r="R39" t="n">
-        <v>6852662</v>
+        <v>6852666</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4792,12 +4831,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4817,7 +4856,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4828,10 +4867,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118679759</v>
+        <v>118679960</v>
       </c>
       <c r="B40" t="n">
-        <v>79565</v>
+        <v>91070</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4840,38 +4879,49 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474450</v>
+        <v>474694</v>
       </c>
       <c r="R40" t="n">
-        <v>6852713</v>
+        <v>6852440</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4906,12 +4956,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Vid hyggeskant</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4934,10 +4990,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118679694</v>
+        <v>118679940</v>
       </c>
       <c r="B41" t="n">
-        <v>78573</v>
+        <v>78129</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4946,25 +5002,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6450</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4974,10 +5030,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474864</v>
+        <v>474472</v>
       </c>
       <c r="R41" t="n">
-        <v>6852352</v>
+        <v>6852583</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5040,10 +5096,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118658677</v>
+        <v>118679642</v>
       </c>
       <c r="B42" t="n">
-        <v>97846</v>
+        <v>79102</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5052,41 +5108,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474572</v>
+        <v>474823</v>
       </c>
       <c r="R42" t="n">
-        <v>6852669</v>
+        <v>6852408</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5110,12 +5166,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5135,7 +5191,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5146,10 +5202,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118679942</v>
+        <v>118679735</v>
       </c>
       <c r="B43" t="n">
-        <v>78129</v>
+        <v>79565</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5162,21 +5218,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5186,10 +5242,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474458</v>
+        <v>474779</v>
       </c>
       <c r="R43" t="n">
-        <v>6852705</v>
+        <v>6852423</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5252,10 +5308,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118680127</v>
+        <v>118679736</v>
       </c>
       <c r="B44" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5264,46 +5320,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474730</v>
+        <v>474798</v>
       </c>
       <c r="R44" t="n">
-        <v>6852558</v>
+        <v>6852414</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5338,18 +5386,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5372,10 +5414,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118680171</v>
+        <v>118679619</v>
       </c>
       <c r="B45" t="n">
-        <v>97846</v>
+        <v>78518</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5384,50 +5426,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474698</v>
+        <v>474495</v>
       </c>
       <c r="R45" t="n">
-        <v>6852578</v>
+        <v>6852672</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5468,7 +5498,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5480,7 +5509,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5491,10 +5520,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118680179</v>
+        <v>118679947</v>
       </c>
       <c r="B46" t="n">
-        <v>97846</v>
+        <v>91779</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5503,50 +5532,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474779</v>
+        <v>474722</v>
       </c>
       <c r="R46" t="n">
-        <v>6852421</v>
+        <v>6852456</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5587,7 +5604,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5610,10 +5626,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118680174</v>
+        <v>118679657</v>
       </c>
       <c r="B47" t="n">
-        <v>97846</v>
+        <v>79102</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5622,46 +5638,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474644</v>
+        <v>474472</v>
       </c>
       <c r="R47" t="n">
-        <v>6852601</v>
+        <v>6852583</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5696,18 +5704,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5730,10 +5732,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118679940</v>
+        <v>118658622</v>
       </c>
       <c r="B48" t="n">
-        <v>78129</v>
+        <v>79566</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5746,37 +5748,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474472</v>
+        <v>474551</v>
       </c>
       <c r="R48" t="n">
-        <v>6852583</v>
+        <v>6852613</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5800,12 +5802,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5825,7 +5827,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5836,10 +5838,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118658643</v>
+        <v>118679694</v>
       </c>
       <c r="B49" t="n">
-        <v>79565</v>
+        <v>78573</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5848,41 +5850,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474573</v>
+        <v>474864</v>
       </c>
       <c r="R49" t="n">
-        <v>6852666</v>
+        <v>6852352</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5906,12 +5908,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5931,7 +5933,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5942,7 +5944,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118680199</v>
+        <v>118680180</v>
       </c>
       <c r="B50" t="n">
         <v>97846</v>
@@ -5975,13 +5977,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
@@ -5990,10 +5996,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474451</v>
+        <v>474813</v>
       </c>
       <c r="R50" t="n">
-        <v>6852701</v>
+        <v>6852408</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6026,11 +6032,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6062,10 +6063,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118679959</v>
+        <v>118680171</v>
       </c>
       <c r="B51" t="n">
-        <v>91779</v>
+        <v>97846</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6074,38 +6075,50 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474464</v>
+        <v>474698</v>
       </c>
       <c r="R51" t="n">
-        <v>6852695</v>
+        <v>6852578</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6146,6 +6159,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6168,7 +6182,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118680169</v>
+        <v>118680128</v>
       </c>
       <c r="B52" t="n">
         <v>97846</v>
@@ -6216,10 +6230,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474444</v>
+        <v>474753</v>
       </c>
       <c r="R52" t="n">
-        <v>6852693</v>
+        <v>6852510</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6256,7 +6270,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>1 blomstjälk, på nyligen upptaget kalhygge, Stora Enso</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6288,10 +6302,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118679642</v>
+        <v>118680174</v>
       </c>
       <c r="B53" t="n">
-        <v>79102</v>
+        <v>97846</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6300,38 +6314,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474823</v>
+        <v>474644</v>
       </c>
       <c r="R53" t="n">
-        <v>6852408</v>
+        <v>6852601</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6366,12 +6388,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6394,10 +6422,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118680138</v>
+        <v>118679618</v>
       </c>
       <c r="B54" t="n">
-        <v>97846</v>
+        <v>78518</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6406,46 +6434,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474928</v>
+        <v>474423</v>
       </c>
       <c r="R54" t="n">
-        <v>6852284</v>
+        <v>6852576</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6480,18 +6500,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6503,7 +6517,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6514,10 +6528,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118680183</v>
+        <v>118679621</v>
       </c>
       <c r="B55" t="n">
-        <v>97846</v>
+        <v>78518</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6526,46 +6540,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474905</v>
+        <v>474466</v>
       </c>
       <c r="R55" t="n">
-        <v>6852317</v>
+        <v>6852701</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6600,18 +6606,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6634,10 +6634,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118679659</v>
+        <v>118679758</v>
       </c>
       <c r="B56" t="n">
-        <v>79102</v>
+        <v>79565</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6650,21 +6650,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6674,10 +6674,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474456</v>
+        <v>474422</v>
       </c>
       <c r="R56" t="n">
-        <v>6852705</v>
+        <v>6852578</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss, Emma Sewell, Jana Eriksson, Ann-Charlotte Svensson, diana spjut, August Lindberg, Klara Li Yngve</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6740,10 +6740,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118679657</v>
+        <v>118679617</v>
       </c>
       <c r="B57" t="n">
-        <v>79102</v>
+        <v>78518</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6756,21 +6756,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6780,10 +6780,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474472</v>
+        <v>474427</v>
       </c>
       <c r="R57" t="n">
-        <v>6852583</v>
+        <v>6852576</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6846,10 +6846,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118658617</v>
+        <v>118679724</v>
       </c>
       <c r="B58" t="n">
-        <v>57443</v>
+        <v>78221</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6862,37 +6862,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474552</v>
+        <v>474329</v>
       </c>
       <c r="R58" t="n">
-        <v>6852613</v>
+        <v>6852451</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6916,12 +6916,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">

--- a/artfynd/A 61561-2021 artfynd.xlsx
+++ b/artfynd/A 61561-2021 artfynd.xlsx
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118680288</v>
+        <v>118682042</v>
       </c>
       <c r="B14" t="n">
-        <v>78518</v>
+        <v>78136</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1996,37 +1996,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Fågelsjö 7 mellan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474435</v>
+        <v>474472</v>
       </c>
       <c r="R14" t="n">
-        <v>6852671</v>
+        <v>6852580</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2070,26 +2070,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Klara Li Yngve</t>
+          <t>August Lindberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klara Li Yngve, Philipp Weiss, Jana Eriksson, August Lindberg, diana spjut, Ann-Charlotte Svensson, Emma Sewell</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>August Lindberg, Jana Eriksson, Philipp Weiss, Klara Li Yngve</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118680304</v>
+        <v>118680319</v>
       </c>
       <c r="B15" t="n">
-        <v>78221</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2098,38 +2094,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474415</v>
+        <v>474434</v>
       </c>
       <c r="R15" t="n">
-        <v>6852671</v>
+        <v>6852667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,6 +2170,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2192,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118682042</v>
+        <v>118680288</v>
       </c>
       <c r="B16" t="n">
-        <v>78129</v>
+        <v>78525</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,37 +2209,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fågelsjö 7 mellan, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474472</v>
+        <v>474435</v>
       </c>
       <c r="R16" t="n">
-        <v>6852580</v>
+        <v>6852671</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2282,22 +2283,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>August Lindberg</t>
+          <t>Klara Li Yngve</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>August Lindberg, Jana Eriksson, Philipp Weiss, Klara Li Yngve</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Klara Li Yngve, Philipp Weiss, Jana Eriksson, August Lindberg, diana spjut, Ann-Charlotte Svensson, Emma Sewell</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>118680321</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118680319</v>
+        <v>118680304</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>78228</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,42 +2422,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474434</v>
+        <v>474415</v>
       </c>
       <c r="R18" t="n">
-        <v>6852667</v>
+        <v>6852671</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,7 +2494,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118680183</v>
+        <v>118679700</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>79476</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2528,46 +2528,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474905</v>
+        <v>474495</v>
       </c>
       <c r="R19" t="n">
-        <v>6852317</v>
+        <v>6852676</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2602,18 +2594,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2636,10 +2622,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118679734</v>
+        <v>118680138</v>
       </c>
       <c r="B20" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2648,38 +2634,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474576</v>
+        <v>474928</v>
       </c>
       <c r="R20" t="n">
-        <v>6852662</v>
+        <v>6852284</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,12 +2708,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118679941</v>
+        <v>118680179</v>
       </c>
       <c r="B21" t="n">
-        <v>78129</v>
+        <v>97853</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2754,38 +2754,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474458</v>
+        <v>474779</v>
       </c>
       <c r="R21" t="n">
-        <v>6852586</v>
+        <v>6852421</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,6 +2838,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2848,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118679959</v>
+        <v>118679734</v>
       </c>
       <c r="B22" t="n">
-        <v>91779</v>
+        <v>79572</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2860,25 +2873,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2888,10 +2901,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474464</v>
+        <v>474576</v>
       </c>
       <c r="R22" t="n">
-        <v>6852695</v>
+        <v>6852662</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2954,10 +2967,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118658617</v>
+        <v>118679657</v>
       </c>
       <c r="B23" t="n">
-        <v>57443</v>
+        <v>79109</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2970,37 +2983,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474552</v>
+        <v>474472</v>
       </c>
       <c r="R23" t="n">
-        <v>6852613</v>
+        <v>6852583</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3024,12 +3037,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,7 +3062,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3060,10 +3073,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118680137</v>
+        <v>118658622</v>
       </c>
       <c r="B24" t="n">
-        <v>97846</v>
+        <v>79573</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3072,49 +3085,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474644</v>
+        <v>474551</v>
       </c>
       <c r="R24" t="n">
-        <v>6852619</v>
+        <v>6852613</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3138,17 +3143,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3157,7 +3157,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3169,7 +3168,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3180,10 +3179,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118658645</v>
+        <v>118680174</v>
       </c>
       <c r="B25" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,41 +3191,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474572</v>
+        <v>474644</v>
       </c>
       <c r="R25" t="n">
-        <v>6852630</v>
+        <v>6852601</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3250,12 +3257,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3264,6 +3276,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3275,7 +3288,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3286,10 +3299,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118680169</v>
+        <v>118679960</v>
       </c>
       <c r="B26" t="n">
-        <v>97846</v>
+        <v>91077</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,31 +3315,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3334,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474444</v>
+        <v>474694</v>
       </c>
       <c r="R26" t="n">
-        <v>6852693</v>
+        <v>6852440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3374,7 +3390,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>Vid hyggeskant</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3406,10 +3422,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118680130</v>
+        <v>118679735</v>
       </c>
       <c r="B27" t="n">
-        <v>97846</v>
+        <v>79572</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3418,46 +3434,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474469</v>
+        <v>474779</v>
       </c>
       <c r="R27" t="n">
-        <v>6852587</v>
+        <v>6852423</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3492,18 +3500,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3526,10 +3528,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118679759</v>
+        <v>118680183</v>
       </c>
       <c r="B28" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3538,38 +3540,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474450</v>
+        <v>474905</v>
       </c>
       <c r="R28" t="n">
-        <v>6852713</v>
+        <v>6852317</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3604,12 +3614,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3621,7 +3637,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Emma Sewell, Jana Eriksson, Ann-Charlotte Svensson, diana spjut, August Lindberg, Klara Li Yngve</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3635,7 +3651,7 @@
         <v>118680127</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3752,10 +3768,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118680138</v>
+        <v>118679947</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>91786</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3764,46 +3780,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474928</v>
+        <v>474722</v>
       </c>
       <c r="R30" t="n">
-        <v>6852284</v>
+        <v>6852456</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3838,18 +3846,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3872,10 +3874,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118679942</v>
+        <v>118679619</v>
       </c>
       <c r="B31" t="n">
-        <v>78129</v>
+        <v>78525</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3888,21 +3890,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3912,10 +3914,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474458</v>
+        <v>474495</v>
       </c>
       <c r="R31" t="n">
-        <v>6852705</v>
+        <v>6852672</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3967,7 +3969,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3978,10 +3980,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118658677</v>
+        <v>118679940</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>78136</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3990,41 +3992,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474572</v>
+        <v>474472</v>
       </c>
       <c r="R32" t="n">
-        <v>6852669</v>
+        <v>6852583</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4048,12 +4050,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4073,7 +4075,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4084,10 +4086,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118680199</v>
+        <v>118679941</v>
       </c>
       <c r="B33" t="n">
-        <v>97846</v>
+        <v>78136</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4096,46 +4098,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474451</v>
+        <v>474458</v>
       </c>
       <c r="R33" t="n">
-        <v>6852701</v>
+        <v>6852586</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4170,18 +4164,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4204,10 +4192,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118680179</v>
+        <v>118680169</v>
       </c>
       <c r="B34" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4237,17 +4225,13 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4256,10 +4240,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474779</v>
+        <v>474444</v>
       </c>
       <c r="R34" t="n">
-        <v>6852421</v>
+        <v>6852693</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4292,6 +4276,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4323,10 +4312,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118680129</v>
+        <v>118679759</v>
       </c>
       <c r="B35" t="n">
-        <v>97846</v>
+        <v>79572</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4335,46 +4324,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474707</v>
+        <v>474450</v>
       </c>
       <c r="R35" t="n">
-        <v>6852573</v>
+        <v>6852713</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4409,18 +4390,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4443,10 +4418,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118679700</v>
+        <v>118679736</v>
       </c>
       <c r="B36" t="n">
-        <v>79469</v>
+        <v>79572</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4455,25 +4430,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4483,10 +4458,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474495</v>
+        <v>474798</v>
       </c>
       <c r="R36" t="n">
-        <v>6852676</v>
+        <v>6852414</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4549,10 +4524,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118679945</v>
+        <v>118680129</v>
       </c>
       <c r="B37" t="n">
-        <v>91779</v>
+        <v>97853</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4561,38 +4536,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474746</v>
+        <v>474707</v>
       </c>
       <c r="R37" t="n">
-        <v>6852534</v>
+        <v>6852573</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4627,12 +4610,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4655,10 +4644,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118679659</v>
+        <v>118680128</v>
       </c>
       <c r="B38" t="n">
-        <v>79102</v>
+        <v>97853</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4667,38 +4656,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474456</v>
+        <v>474753</v>
       </c>
       <c r="R38" t="n">
-        <v>6852705</v>
+        <v>6852510</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4733,12 +4730,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>1 blomstjälk, på nyligen upptaget kalhygge, Stora Enso</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4761,10 +4764,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118658643</v>
+        <v>118679618</v>
       </c>
       <c r="B39" t="n">
-        <v>79565</v>
+        <v>78525</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4777,37 +4780,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474573</v>
+        <v>474423</v>
       </c>
       <c r="R39" t="n">
-        <v>6852666</v>
+        <v>6852576</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4831,12 +4834,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4867,10 +4870,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118679960</v>
+        <v>118679659</v>
       </c>
       <c r="B40" t="n">
-        <v>91070</v>
+        <v>79109</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4879,49 +4882,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>760</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474694</v>
+        <v>474456</v>
       </c>
       <c r="R40" t="n">
-        <v>6852440</v>
+        <v>6852705</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4956,18 +4948,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Vid hyggeskant</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4990,10 +4976,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118679940</v>
+        <v>118679945</v>
       </c>
       <c r="B41" t="n">
-        <v>78129</v>
+        <v>91786</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5002,25 +4988,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5030,10 +5016,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474472</v>
+        <v>474746</v>
       </c>
       <c r="R41" t="n">
-        <v>6852583</v>
+        <v>6852534</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5096,10 +5082,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118679642</v>
+        <v>118679758</v>
       </c>
       <c r="B42" t="n">
-        <v>79102</v>
+        <v>79572</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5112,21 +5098,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5136,10 +5122,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474823</v>
+        <v>474422</v>
       </c>
       <c r="R42" t="n">
-        <v>6852408</v>
+        <v>6852578</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5202,10 +5188,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118679735</v>
+        <v>118679942</v>
       </c>
       <c r="B43" t="n">
-        <v>79565</v>
+        <v>78136</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5218,21 +5204,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5242,10 +5228,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474779</v>
+        <v>474458</v>
       </c>
       <c r="R43" t="n">
-        <v>6852423</v>
+        <v>6852705</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5308,10 +5294,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118679736</v>
+        <v>118680137</v>
       </c>
       <c r="B44" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5320,38 +5306,46 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474798</v>
+        <v>474644</v>
       </c>
       <c r="R44" t="n">
-        <v>6852414</v>
+        <v>6852619</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5386,12 +5380,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5414,10 +5414,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118679619</v>
+        <v>118658645</v>
       </c>
       <c r="B45" t="n">
-        <v>78518</v>
+        <v>79572</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5430,37 +5430,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474495</v>
+        <v>474572</v>
       </c>
       <c r="R45" t="n">
-        <v>6852672</v>
+        <v>6852630</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5484,12 +5484,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5520,10 +5520,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118679947</v>
+        <v>118680130</v>
       </c>
       <c r="B46" t="n">
-        <v>91779</v>
+        <v>97853</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5532,38 +5532,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474722</v>
+        <v>474469</v>
       </c>
       <c r="R46" t="n">
-        <v>6852456</v>
+        <v>6852587</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5598,12 +5606,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5626,10 +5640,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118679657</v>
+        <v>118679724</v>
       </c>
       <c r="B47" t="n">
-        <v>79102</v>
+        <v>78228</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5642,21 +5656,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5666,10 +5680,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474472</v>
+        <v>474329</v>
       </c>
       <c r="R47" t="n">
-        <v>6852583</v>
+        <v>6852451</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5732,10 +5746,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118658622</v>
+        <v>118680171</v>
       </c>
       <c r="B48" t="n">
-        <v>79566</v>
+        <v>97853</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5744,41 +5758,53 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474551</v>
+        <v>474698</v>
       </c>
       <c r="R48" t="n">
-        <v>6852613</v>
+        <v>6852578</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5802,12 +5828,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5816,6 +5842,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5827,7 +5854,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5838,10 +5865,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118679694</v>
+        <v>118658617</v>
       </c>
       <c r="B49" t="n">
-        <v>78573</v>
+        <v>57443</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5850,41 +5877,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6450</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474864</v>
+        <v>474552</v>
       </c>
       <c r="R49" t="n">
-        <v>6852352</v>
+        <v>6852613</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5908,12 +5935,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5933,7 +5960,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5944,10 +5971,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118680180</v>
+        <v>118679959</v>
       </c>
       <c r="B50" t="n">
-        <v>97846</v>
+        <v>91786</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5956,50 +5983,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474813</v>
+        <v>474464</v>
       </c>
       <c r="R50" t="n">
-        <v>6852408</v>
+        <v>6852695</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6040,7 +6055,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6063,10 +6077,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118680171</v>
+        <v>118658677</v>
       </c>
       <c r="B51" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6096,32 +6110,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474698</v>
+        <v>474572</v>
       </c>
       <c r="R51" t="n">
-        <v>6852578</v>
+        <v>6852669</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6145,12 +6147,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6159,7 +6161,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6171,7 +6172,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6182,10 +6183,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118680128</v>
+        <v>118680199</v>
       </c>
       <c r="B52" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6230,10 +6231,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474753</v>
+        <v>474451</v>
       </c>
       <c r="R52" t="n">
-        <v>6852510</v>
+        <v>6852701</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6270,7 +6271,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>1 blomstjälk, på nyligen upptaget kalhygge, Stora Enso</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6302,10 +6303,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118680174</v>
+        <v>118679617</v>
       </c>
       <c r="B53" t="n">
-        <v>97846</v>
+        <v>78525</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6314,46 +6315,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474644</v>
+        <v>474427</v>
       </c>
       <c r="R53" t="n">
-        <v>6852601</v>
+        <v>6852576</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6388,18 +6381,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6411,7 +6398,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6422,10 +6409,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118679618</v>
+        <v>118679642</v>
       </c>
       <c r="B54" t="n">
-        <v>78518</v>
+        <v>79109</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6438,21 +6425,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6462,10 +6449,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474423</v>
+        <v>474823</v>
       </c>
       <c r="R54" t="n">
-        <v>6852576</v>
+        <v>6852408</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6517,7 +6504,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6528,10 +6515,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118679621</v>
+        <v>118679694</v>
       </c>
       <c r="B55" t="n">
-        <v>78518</v>
+        <v>78580</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6540,25 +6527,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6450</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6568,10 +6555,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474466</v>
+        <v>474864</v>
       </c>
       <c r="R55" t="n">
-        <v>6852701</v>
+        <v>6852352</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6623,7 +6610,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6634,10 +6621,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118679758</v>
+        <v>118679621</v>
       </c>
       <c r="B56" t="n">
-        <v>79565</v>
+        <v>78525</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6650,21 +6637,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6674,10 +6661,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474422</v>
+        <v>474466</v>
       </c>
       <c r="R56" t="n">
-        <v>6852578</v>
+        <v>6852701</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6729,7 +6716,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Emma Sewell, Jana Eriksson, Ann-Charlotte Svensson, diana spjut, August Lindberg, Klara Li Yngve</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6740,10 +6727,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118679617</v>
+        <v>118658643</v>
       </c>
       <c r="B57" t="n">
-        <v>78518</v>
+        <v>79572</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6756,37 +6743,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474427</v>
+        <v>474573</v>
       </c>
       <c r="R57" t="n">
-        <v>6852576</v>
+        <v>6852666</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6810,12 +6797,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6846,10 +6833,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118679724</v>
+        <v>118680180</v>
       </c>
       <c r="B58" t="n">
-        <v>78221</v>
+        <v>97853</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6858,38 +6845,50 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474329</v>
+        <v>474813</v>
       </c>
       <c r="R58" t="n">
-        <v>6852451</v>
+        <v>6852408</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6930,6 +6929,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61561-2021 artfynd.xlsx
+++ b/artfynd/A 61561-2021 artfynd.xlsx
@@ -2967,10 +2967,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118679657</v>
+        <v>118658622</v>
       </c>
       <c r="B23" t="n">
-        <v>79109</v>
+        <v>79573</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2983,37 +2983,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474472</v>
+        <v>474551</v>
       </c>
       <c r="R23" t="n">
-        <v>6852583</v>
+        <v>6852613</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3073,10 +3073,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118658622</v>
+        <v>118679657</v>
       </c>
       <c r="B24" t="n">
-        <v>79573</v>
+        <v>79109</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3089,37 +3089,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474551</v>
+        <v>474472</v>
       </c>
       <c r="R24" t="n">
-        <v>6852613</v>
+        <v>6852583</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3143,12 +3143,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118679736</v>
+        <v>118680129</v>
       </c>
       <c r="B36" t="n">
-        <v>79572</v>
+        <v>97853</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4430,38 +4430,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474798</v>
+        <v>474707</v>
       </c>
       <c r="R36" t="n">
-        <v>6852414</v>
+        <v>6852573</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4496,12 +4504,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4524,10 +4538,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118680129</v>
+        <v>118679736</v>
       </c>
       <c r="B37" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4536,46 +4550,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474707</v>
+        <v>474798</v>
       </c>
       <c r="R37" t="n">
-        <v>6852573</v>
+        <v>6852414</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4610,18 +4616,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -6621,10 +6621,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118679621</v>
+        <v>118680180</v>
       </c>
       <c r="B56" t="n">
-        <v>78525</v>
+        <v>97853</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6633,38 +6633,50 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474466</v>
+        <v>474813</v>
       </c>
       <c r="R56" t="n">
-        <v>6852701</v>
+        <v>6852408</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6705,6 +6717,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6716,7 +6729,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6727,10 +6740,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118658643</v>
+        <v>118679621</v>
       </c>
       <c r="B57" t="n">
-        <v>79572</v>
+        <v>78525</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6743,37 +6756,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474573</v>
+        <v>474466</v>
       </c>
       <c r="R57" t="n">
-        <v>6852666</v>
+        <v>6852701</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6797,12 +6810,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6833,10 +6846,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118680180</v>
+        <v>118658643</v>
       </c>
       <c r="B58" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6845,53 +6858,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474813</v>
+        <v>474573</v>
       </c>
       <c r="R58" t="n">
-        <v>6852408</v>
+        <v>6852666</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6915,12 +6916,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6929,7 +6930,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">

--- a/artfynd/A 61561-2021 artfynd.xlsx
+++ b/artfynd/A 61561-2021 artfynd.xlsx
@@ -2082,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118680319</v>
+        <v>118680288</v>
       </c>
       <c r="B15" t="n">
-        <v>97853</v>
+        <v>78525</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,42 +2094,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474434</v>
+        <v>474435</v>
       </c>
       <c r="R15" t="n">
-        <v>6852667</v>
+        <v>6852671</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2166,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2193,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118680288</v>
+        <v>118680319</v>
       </c>
       <c r="B16" t="n">
-        <v>78525</v>
+        <v>97853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,38 +2200,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474435</v>
+        <v>474434</v>
       </c>
       <c r="R16" t="n">
-        <v>6852671</v>
+        <v>6852667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,6 +2276,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118679700</v>
+        <v>118680137</v>
       </c>
       <c r="B19" t="n">
-        <v>79476</v>
+        <v>97853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2528,38 +2528,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474495</v>
+        <v>474644</v>
       </c>
       <c r="R19" t="n">
-        <v>6852676</v>
+        <v>6852619</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,12 +2602,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2622,10 +2636,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118680138</v>
+        <v>118679758</v>
       </c>
       <c r="B20" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,46 +2648,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474928</v>
+        <v>474422</v>
       </c>
       <c r="R20" t="n">
-        <v>6852284</v>
+        <v>6852578</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,18 +2714,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118680179</v>
+        <v>118679694</v>
       </c>
       <c r="B21" t="n">
-        <v>97853</v>
+        <v>78580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2754,50 +2754,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474779</v>
+        <v>474864</v>
       </c>
       <c r="R21" t="n">
-        <v>6852421</v>
+        <v>6852352</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2838,7 +2826,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2861,10 +2848,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118679734</v>
+        <v>118679617</v>
       </c>
       <c r="B22" t="n">
-        <v>79572</v>
+        <v>78525</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2877,21 +2864,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2901,10 +2888,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474576</v>
+        <v>474427</v>
       </c>
       <c r="R22" t="n">
-        <v>6852662</v>
+        <v>6852576</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2956,7 +2943,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3073,10 +3060,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118679657</v>
+        <v>118679736</v>
       </c>
       <c r="B24" t="n">
-        <v>79109</v>
+        <v>79572</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3089,21 +3076,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3113,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474472</v>
+        <v>474798</v>
       </c>
       <c r="R24" t="n">
-        <v>6852583</v>
+        <v>6852414</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3179,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118680174</v>
+        <v>118679947</v>
       </c>
       <c r="B25" t="n">
-        <v>97853</v>
+        <v>91786</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3191,46 +3178,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474644</v>
+        <v>474722</v>
       </c>
       <c r="R25" t="n">
-        <v>6852601</v>
+        <v>6852456</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3265,18 +3244,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3299,10 +3272,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118679960</v>
+        <v>118680127</v>
       </c>
       <c r="B26" t="n">
-        <v>91077</v>
+        <v>97853</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3315,34 +3288,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3350,10 +3320,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474694</v>
+        <v>474730</v>
       </c>
       <c r="R26" t="n">
-        <v>6852440</v>
+        <v>6852558</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3390,7 +3360,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Vid hyggeskant</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3528,7 +3498,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118680183</v>
+        <v>118658677</v>
       </c>
       <c r="B28" t="n">
         <v>97853</v>
@@ -3562,27 +3532,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474905</v>
+        <v>474572</v>
       </c>
       <c r="R28" t="n">
-        <v>6852317</v>
+        <v>6852669</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3606,17 +3568,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3625,7 +3582,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3637,7 +3593,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3648,7 +3604,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118680127</v>
+        <v>118680180</v>
       </c>
       <c r="B29" t="n">
         <v>97853</v>
@@ -3681,13 +3637,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3696,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474730</v>
+        <v>474813</v>
       </c>
       <c r="R29" t="n">
-        <v>6852558</v>
+        <v>6852408</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3732,11 +3692,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3768,10 +3723,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118679947</v>
+        <v>118680179</v>
       </c>
       <c r="B30" t="n">
-        <v>91786</v>
+        <v>97853</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3780,38 +3735,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474722</v>
+        <v>474779</v>
       </c>
       <c r="R30" t="n">
-        <v>6852456</v>
+        <v>6852421</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3852,6 +3819,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3874,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118679619</v>
+        <v>118679941</v>
       </c>
       <c r="B31" t="n">
-        <v>78525</v>
+        <v>78136</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3890,21 +3858,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3914,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474495</v>
+        <v>474458</v>
       </c>
       <c r="R31" t="n">
-        <v>6852672</v>
+        <v>6852586</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3969,7 +3937,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3980,10 +3948,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118679940</v>
+        <v>118679619</v>
       </c>
       <c r="B32" t="n">
-        <v>78136</v>
+        <v>78525</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3996,21 +3964,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4020,10 +3988,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474472</v>
+        <v>474495</v>
       </c>
       <c r="R32" t="n">
-        <v>6852583</v>
+        <v>6852672</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4075,7 +4043,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4086,10 +4054,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118679941</v>
+        <v>118680130</v>
       </c>
       <c r="B33" t="n">
-        <v>78136</v>
+        <v>97853</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4098,38 +4066,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474458</v>
+        <v>474469</v>
       </c>
       <c r="R33" t="n">
-        <v>6852586</v>
+        <v>6852587</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4164,12 +4140,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4192,7 +4174,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118680169</v>
+        <v>118680183</v>
       </c>
       <c r="B34" t="n">
         <v>97853</v>
@@ -4240,10 +4222,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474444</v>
+        <v>474905</v>
       </c>
       <c r="R34" t="n">
-        <v>6852693</v>
+        <v>6852317</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4280,7 +4262,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4312,10 +4294,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118679759</v>
+        <v>118679618</v>
       </c>
       <c r="B35" t="n">
-        <v>79572</v>
+        <v>78525</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4328,21 +4310,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4352,10 +4334,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474450</v>
+        <v>474423</v>
       </c>
       <c r="R35" t="n">
-        <v>6852713</v>
+        <v>6852576</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4407,7 +4389,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4418,10 +4400,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118680129</v>
+        <v>118658617</v>
       </c>
       <c r="B36" t="n">
-        <v>97853</v>
+        <v>57443</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4430,49 +4412,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474707</v>
+        <v>474552</v>
       </c>
       <c r="R36" t="n">
-        <v>6852573</v>
+        <v>6852613</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4496,17 +4470,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4515,7 +4484,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4527,7 +4495,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4538,7 +4506,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118679736</v>
+        <v>118679734</v>
       </c>
       <c r="B37" t="n">
         <v>79572</v>
@@ -4578,10 +4546,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474798</v>
+        <v>474576</v>
       </c>
       <c r="R37" t="n">
-        <v>6852414</v>
+        <v>6852662</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4644,10 +4612,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118680128</v>
+        <v>118658645</v>
       </c>
       <c r="B38" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4656,49 +4624,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474753</v>
+        <v>474572</v>
       </c>
       <c r="R38" t="n">
-        <v>6852510</v>
+        <v>6852630</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4722,17 +4682,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>1 blomstjälk, på nyligen upptaget kalhygge, Stora Enso</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4741,7 +4696,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4753,7 +4707,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4764,7 +4718,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118679618</v>
+        <v>118679621</v>
       </c>
       <c r="B39" t="n">
         <v>78525</v>
@@ -4804,10 +4758,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474423</v>
+        <v>474466</v>
       </c>
       <c r="R39" t="n">
-        <v>6852576</v>
+        <v>6852701</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4870,10 +4824,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118679659</v>
+        <v>118679960</v>
       </c>
       <c r="B40" t="n">
-        <v>79109</v>
+        <v>91077</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4882,38 +4836,49 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>760</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474456</v>
+        <v>474694</v>
       </c>
       <c r="R40" t="n">
-        <v>6852705</v>
+        <v>6852440</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4948,12 +4913,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Vid hyggeskant</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4976,10 +4947,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118679945</v>
+        <v>118679724</v>
       </c>
       <c r="B41" t="n">
-        <v>91786</v>
+        <v>78228</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4988,25 +4959,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5016,10 +4987,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474746</v>
+        <v>474329</v>
       </c>
       <c r="R41" t="n">
-        <v>6852534</v>
+        <v>6852451</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5082,10 +5053,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118679758</v>
+        <v>118679659</v>
       </c>
       <c r="B42" t="n">
-        <v>79572</v>
+        <v>79109</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5098,21 +5069,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5122,10 +5093,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474422</v>
+        <v>474456</v>
       </c>
       <c r="R42" t="n">
-        <v>6852578</v>
+        <v>6852705</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5188,10 +5159,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118679942</v>
+        <v>118658643</v>
       </c>
       <c r="B43" t="n">
-        <v>78136</v>
+        <v>79572</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5204,37 +5175,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hällstjärnen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474458</v>
+        <v>474573</v>
       </c>
       <c r="R43" t="n">
-        <v>6852705</v>
+        <v>6852666</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5258,12 +5229,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5283,7 +5254,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5294,10 +5265,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118680137</v>
+        <v>118679945</v>
       </c>
       <c r="B44" t="n">
-        <v>97853</v>
+        <v>91786</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5306,46 +5277,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474644</v>
+        <v>474746</v>
       </c>
       <c r="R44" t="n">
-        <v>6852619</v>
+        <v>6852534</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5380,18 +5343,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5414,10 +5371,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118658645</v>
+        <v>118680169</v>
       </c>
       <c r="B45" t="n">
-        <v>79572</v>
+        <v>97853</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5426,41 +5383,49 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474572</v>
+        <v>474444</v>
       </c>
       <c r="R45" t="n">
-        <v>6852630</v>
+        <v>6852693</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5484,12 +5449,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5498,6 +5468,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5509,7 +5480,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5520,7 +5491,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118680130</v>
+        <v>118680129</v>
       </c>
       <c r="B46" t="n">
         <v>97853</v>
@@ -5568,10 +5539,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474469</v>
+        <v>474707</v>
       </c>
       <c r="R46" t="n">
-        <v>6852587</v>
+        <v>6852573</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5640,10 +5611,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118679724</v>
+        <v>118680174</v>
       </c>
       <c r="B47" t="n">
-        <v>78228</v>
+        <v>97853</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5652,38 +5623,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474329</v>
+        <v>474644</v>
       </c>
       <c r="R47" t="n">
-        <v>6852451</v>
+        <v>6852601</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5718,12 +5697,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5746,10 +5731,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118680171</v>
+        <v>118679940</v>
       </c>
       <c r="B48" t="n">
-        <v>97853</v>
+        <v>78136</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5758,50 +5743,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474698</v>
+        <v>474472</v>
       </c>
       <c r="R48" t="n">
-        <v>6852578</v>
+        <v>6852583</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5842,7 +5815,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5865,10 +5837,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118658617</v>
+        <v>118680171</v>
       </c>
       <c r="B49" t="n">
-        <v>57443</v>
+        <v>97853</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5877,41 +5849,53 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474552</v>
+        <v>474698</v>
       </c>
       <c r="R49" t="n">
-        <v>6852613</v>
+        <v>6852578</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5935,12 +5919,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5949,6 +5933,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5960,7 +5945,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5971,10 +5956,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118679959</v>
+        <v>118680199</v>
       </c>
       <c r="B50" t="n">
-        <v>91786</v>
+        <v>97853</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5983,38 +5968,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474464</v>
+        <v>474451</v>
       </c>
       <c r="R50" t="n">
-        <v>6852695</v>
+        <v>6852701</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6049,12 +6042,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6077,10 +6076,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118658677</v>
+        <v>118679942</v>
       </c>
       <c r="B51" t="n">
-        <v>97853</v>
+        <v>78136</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6089,41 +6088,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474572</v>
+        <v>474458</v>
       </c>
       <c r="R51" t="n">
-        <v>6852669</v>
+        <v>6852705</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6147,12 +6146,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6172,7 +6171,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6183,10 +6182,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118680199</v>
+        <v>118679700</v>
       </c>
       <c r="B52" t="n">
-        <v>97853</v>
+        <v>79476</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6195,46 +6194,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474451</v>
+        <v>474495</v>
       </c>
       <c r="R52" t="n">
-        <v>6852701</v>
+        <v>6852676</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6269,18 +6260,12 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6303,10 +6288,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118679617</v>
+        <v>118679657</v>
       </c>
       <c r="B53" t="n">
-        <v>78525</v>
+        <v>79109</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6319,21 +6304,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6343,10 +6328,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474427</v>
+        <v>474472</v>
       </c>
       <c r="R53" t="n">
-        <v>6852576</v>
+        <v>6852583</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6398,7 +6383,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6409,10 +6394,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118679642</v>
+        <v>118679759</v>
       </c>
       <c r="B54" t="n">
-        <v>79109</v>
+        <v>79572</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6425,21 +6410,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6449,10 +6434,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474823</v>
+        <v>474450</v>
       </c>
       <c r="R54" t="n">
-        <v>6852408</v>
+        <v>6852713</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6515,10 +6500,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118679694</v>
+        <v>118680138</v>
       </c>
       <c r="B55" t="n">
-        <v>78580</v>
+        <v>97853</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6527,38 +6512,46 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474864</v>
+        <v>474928</v>
       </c>
       <c r="R55" t="n">
-        <v>6852352</v>
+        <v>6852284</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6593,12 +6586,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6621,10 +6620,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118680180</v>
+        <v>118679642</v>
       </c>
       <c r="B56" t="n">
-        <v>97853</v>
+        <v>79109</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6633,47 +6632,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474813</v>
+        <v>474823</v>
       </c>
       <c r="R56" t="n">
         <v>6852408</v>
@@ -6717,7 +6704,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6740,10 +6726,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118679621</v>
+        <v>118680128</v>
       </c>
       <c r="B57" t="n">
-        <v>78525</v>
+        <v>97853</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6752,38 +6738,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474466</v>
+        <v>474753</v>
       </c>
       <c r="R57" t="n">
-        <v>6852701</v>
+        <v>6852510</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6818,12 +6812,18 @@
           <t>2024-07-25</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>1 blomstjälk, på nyligen upptaget kalhygge, Stora Enso</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6846,10 +6846,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118658643</v>
+        <v>118679959</v>
       </c>
       <c r="B58" t="n">
-        <v>79572</v>
+        <v>91786</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6858,41 +6858,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hällstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474573</v>
+        <v>474464</v>
       </c>
       <c r="R58" t="n">
-        <v>6852666</v>
+        <v>6852695</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6916,12 +6916,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Klara Li Yngve, August Lindberg, diana spjut, Ann-Charlotte Svensson, Jana Eriksson, Emma Sewell</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">

--- a/artfynd/A 61561-2021 artfynd.xlsx
+++ b/artfynd/A 61561-2021 artfynd.xlsx
@@ -6182,7 +6182,7 @@
         <v>118679960</v>
       </c>
       <c r="B52" t="n">
-        <v>91249</v>
+        <v>91259</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 61561-2021 artfynd.xlsx
+++ b/artfynd/A 61561-2021 artfynd.xlsx
@@ -6182,7 +6182,7 @@
         <v>118679960</v>
       </c>
       <c r="B52" t="n">
-        <v>91259</v>
+        <v>91271</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 61561-2021 artfynd.xlsx
+++ b/artfynd/A 61561-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY138"/>
+  <dimension ref="A1:AZ138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679615</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679617</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679618</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679619</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679621</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679623</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679625</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680288</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679927</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679928</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679929</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679930</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679933</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679939</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679940</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679941</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679942</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679943</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2587,6 +2682,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682042</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2688,6 +2788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679769</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2790,6 +2895,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679866</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2891,6 +3001,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658622</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2993,6 +3108,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679865</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3094,6 +3214,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679954</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3195,6 +3320,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679959</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3292,6 +3422,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682049</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3393,6 +3528,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658711</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3494,6 +3634,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679874</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3595,6 +3740,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679883</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3696,6 +3846,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679884</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3797,6 +3952,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679885</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3898,6 +4058,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679886</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3999,6 +4164,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679887</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4100,6 +4270,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679901</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4201,6 +4376,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679902</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4302,6 +4482,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679778</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4403,6 +4588,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679780</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4504,6 +4694,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680317</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4605,6 +4800,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680318</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4706,6 +4906,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679692</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4807,6 +5012,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679693</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4908,6 +5118,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679650</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5009,6 +5224,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679651</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5110,6 +5330,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679652</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5211,6 +5436,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679653</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5312,6 +5542,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679655</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5413,6 +5648,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679656</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5514,6 +5754,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679657</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5615,6 +5860,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679658</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5716,6 +5966,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679659</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5817,6 +6072,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680291</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5918,6 +6178,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679700</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6019,6 +6284,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658643</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6120,6 +6390,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658645</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6221,6 +6496,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658647</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6322,6 +6602,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679734</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6423,6 +6708,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679751</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6524,6 +6814,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679756</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6625,6 +6920,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679758</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6726,6 +7026,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679759</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6827,6 +7132,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658618</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6928,6 +7238,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679764</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7029,6 +7344,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679962</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7143,6 +7463,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679670</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7260,6 +7585,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658616</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7361,6 +7691,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658617</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7462,6 +7797,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658677</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7563,6 +7903,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658678</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7673,6 +8018,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658680</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7774,6 +8124,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658681</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7875,6 +8230,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658682</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7976,6 +8336,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658683</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8086,6 +8451,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658684</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8201,6 +8571,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680130</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8316,6 +8691,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680135</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8431,6 +8811,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680136</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8546,6 +8931,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680137</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8661,6 +9051,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680161</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8776,6 +9171,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680165</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8891,6 +9291,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680166</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9006,6 +9411,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680169</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9121,6 +9531,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680174</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9236,6 +9651,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680182</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9351,6 +9771,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680191</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9452,6 +9877,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680194</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9567,6 +9997,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680198</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9682,6 +10117,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680199</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9797,6 +10237,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680200</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9898,6 +10343,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680207</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10004,6 +10454,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680319</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10110,6 +10565,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680320</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10216,6 +10676,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680321</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10313,6 +10778,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682031</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10414,6 +10884,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679766</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10515,6 +10990,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658627</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10616,6 +11096,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679717</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10717,6 +11202,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679720</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10818,6 +11308,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679721</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10919,6 +11414,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679724</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11020,6 +11520,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679727</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11121,6 +11626,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679728</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11222,6 +11732,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679729</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11323,6 +11838,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680303</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11424,6 +11944,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680304</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11521,6 +12046,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118681981</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11618,6 +12148,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118681982</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11715,6 +12250,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118681987</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11816,6 +12356,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679663</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11934,6 +12479,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679960</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12035,6 +12585,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679945</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12134,6 +12689,11 @@
       <c r="AY112" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679947</t>
         </is>
       </c>
     </row>
@@ -12237,6 +12797,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117826698</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12338,6 +12903,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117826802</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12439,6 +13009,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117826795</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12540,6 +13115,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679694</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12639,6 +13219,11 @@
       <c r="AY117" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679642</t>
         </is>
       </c>
     </row>
@@ -12742,6 +13327,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117826832</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12843,6 +13433,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117826893</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12944,6 +13539,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679735</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13043,6 +13643,11 @@
       <c r="AY121" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118679736</t>
         </is>
       </c>
     </row>
@@ -13146,6 +13751,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117826945</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13247,6 +13857,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117826707</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13357,6 +13972,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117826610</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13467,6 +14087,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117826636</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13569,6 +14194,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117826798</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13676,6 +14306,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117826799</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13783,6 +14418,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117826800</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13890,6 +14530,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117826801</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14005,6 +14650,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680127</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14120,6 +14770,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680128</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14235,6 +14890,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680129</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14350,6 +15010,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680138</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14464,6 +15129,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680171</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14578,6 +15248,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680179</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14692,6 +15367,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680180</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14807,6 +15487,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680183</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14904,8 +15589,152 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117826796</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>